--- a/diseases/d214/2026-2029.xlsx
+++ b/diseases/d214/2026-2029.xlsx
@@ -1172,7 +1172,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13868,7 +13868,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14270,7 +14270,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">

--- a/diseases/d214/2026-2029.xlsx
+++ b/diseases/d214/2026-2029.xlsx
@@ -1172,7 +1172,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13868,7 +13868,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14270,7 +14270,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">

--- a/diseases/d214/2026-2029.xlsx
+++ b/diseases/d214/2026-2029.xlsx
@@ -14751,6 +14751,408 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection (excluding rabies)</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14784,7 +15186,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -14867,7 +15269,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -14877,7 +15279,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -14897,7 +15299,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d214/2026-2029.xlsx
+++ b/diseases/d214/2026-2029.xlsx
@@ -930,9 +930,6 @@
       <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1182,7 +1179,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -1584,7 +1581,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -1986,7 +1983,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2388,7 +2385,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2952,7 +2949,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3354,7 +3351,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3756,7 +3753,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4158,7 +4155,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4722,7 +4719,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5124,7 +5121,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -5526,7 +5523,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -5928,7 +5925,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6330,7 +6327,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -6477,9 +6474,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -6894,7 +6888,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7296,7 +7290,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7698,7 +7692,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8100,7 +8094,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8247,9 +8241,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -8664,7 +8655,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -9066,7 +9057,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -9468,7 +9459,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -9870,7 +9861,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -10272,7 +10263,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN50" t="b">
@@ -10419,9 +10410,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -10818,9 +10806,6 @@
       <c r="P53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -11070,7 +11055,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -11220,9 +11205,6 @@
       <c r="P55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -11472,7 +11454,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -11622,9 +11604,6 @@
       <c r="P57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -11874,7 +11853,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -12024,9 +12003,6 @@
       <c r="P59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -12276,7 +12252,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -12423,9 +12399,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -12822,9 +12795,6 @@
       <c r="P63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -13074,7 +13044,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -13224,9 +13194,6 @@
       <c r="P65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -13476,7 +13443,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -13626,9 +13593,6 @@
       <c r="P67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -13878,7 +13842,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -14028,9 +13992,6 @@
       <c r="P69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -14280,7 +14241,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -14427,9 +14388,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -14826,9 +14784,6 @@
       <c r="P73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -15078,7 +15033,7 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN74" t="b">

--- a/diseases/d214/2026-2029.xlsx
+++ b/diseases/d214/2026-2029.xlsx
@@ -15108,6 +15108,405 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection (excluding rabies)</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN76" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15141,7 +15540,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -15224,7 +15623,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -15234,7 +15633,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11">
@@ -15254,7 +15653,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d214/2026-2029.xlsx
+++ b/diseases/d214/2026-2029.xlsx
@@ -10656,7 +10656,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN72" t="b">

--- a/diseases/d214/2026-2029.xlsx
+++ b/diseases/d214/2026-2029.xlsx
@@ -15507,6 +15507,405 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection (excluding rabies)</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN78" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15540,7 +15939,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -15623,7 +16022,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -15633,7 +16032,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11">
@@ -15653,7 +16052,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d214/2026-2029.xlsx
+++ b/diseases/d214/2026-2029.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14231,7 +14231,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15023,7 +15023,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">

--- a/diseases/d214/2026-2029.xlsx
+++ b/diseases/d214/2026-2029.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14231,7 +14231,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15023,7 +15023,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">

--- a/diseases/d214/2026-2029.xlsx
+++ b/diseases/d214/2026-2029.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14231,7 +14231,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15023,7 +15023,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">

--- a/diseases/d214/2026-2029.xlsx
+++ b/diseases/d214/2026-2029.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14231,7 +14231,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15023,7 +15023,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">

--- a/diseases/d214/2026-2029.xlsx
+++ b/diseases/d214/2026-2029.xlsx
@@ -10759,12 +10759,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -10803,93 +10803,73 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>weekly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ53" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10916,17 +10896,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -10951,7 +10931,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -10965,168 +10945,73 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>Lyssavirus infection (excluding rabies)</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD54" t="inlineStr">
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG54" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN54" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP54" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ54" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS54" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV54" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11043,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -11188,7 +11073,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -11202,93 +11087,73 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>weekly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ55" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11315,17 +11180,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -11350,7 +11215,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -11364,168 +11229,73 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>Lyssavirus infection (excluding rabies)</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD56" t="inlineStr">
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG56" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP56" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ56" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV56" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11557,12 +11327,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -11587,7 +11357,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -11601,93 +11371,73 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>weekly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ57" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11714,17 +11464,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -11749,7 +11499,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -11763,168 +11513,73 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>Lyssavirus infection (excluding rabies)</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD58" t="inlineStr">
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE58" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG58" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN58" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP58" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ58" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV58" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11956,12 +11611,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -11986,7 +11641,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -12000,93 +11655,73 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>weekly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ59" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12113,17 +11748,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -12148,7 +11783,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -12162,168 +11797,73 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>Lyssavirus infection (excluding rabies)</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD60" t="inlineStr">
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG60" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN60" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP60" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV60" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12355,12 +11895,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -12385,12 +11925,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -12399,6 +11939,9 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -12409,17 +11952,17 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SER_AU_ABLV_MONTHLY</t>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
@@ -12429,12 +11972,12 @@
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>SER_AU_ABLV_MONTHLY</t>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
         </is>
       </c>
       <c r="AT61" t="n">
@@ -12442,47 +11985,47 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12514,12 +12057,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -12544,12 +12087,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -12558,24 +12101,27 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>SER_AU_ABLV_MONTHLY</t>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>SER_AU_ABLV_MONTHLY</t>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Australian bat lyssavirus infection</t>
+          <t>Lyssavirus infection (excluding rabies)</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -12590,7 +12136,7 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
@@ -12600,7 +12146,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
@@ -12610,12 +12156,12 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>narrower</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG62" t="inlineStr">
@@ -12635,12 +12181,12 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>AU_NINDSS_current</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Australia NINDSS human Australian bat lyssavirus infection; explicitly distinct from rabies virus infection.</t>
+          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
@@ -12653,7 +12199,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
@@ -12663,12 +12209,12 @@
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>SER_AU_ABLV_MONTHLY</t>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
         </is>
       </c>
       <c r="AT62" t="n">
@@ -12676,47 +12222,47 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12778,12 +12324,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -12940,12 +12486,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -13177,12 +12723,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -13339,12 +12885,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -13576,12 +13122,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -13738,12 +13284,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -13945,12 +13491,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -13975,7 +13521,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -13989,9 +13535,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -14002,17 +13545,17 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+          <t>SER_AU_ABLV_MONTHLY</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
@@ -14022,12 +13565,12 @@
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+          <t>SER_AU_ABLV_MONTHLY</t>
         </is>
       </c>
       <c r="AT69" t="n">
@@ -14035,47 +13578,47 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14107,12 +13650,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -14137,7 +13680,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -14151,27 +13694,24 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+          <t>SER_AU_ABLV_MONTHLY</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+          <t>SER_AU_ABLV_MONTHLY</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_AU_NINDSS</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Lyssavirus infection (excluding rabies)</t>
+          <t>Australian bat lyssavirus infection</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -14186,7 +13726,7 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
@@ -14196,7 +13736,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:AU:national</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr">
@@ -14206,12 +13746,12 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG70" t="inlineStr">
@@ -14231,12 +13771,12 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>AU_NINDSS_current</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
+          <t>Australia NINDSS human Australian bat lyssavirus infection; explicitly distinct from rabies virus infection.</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
@@ -14249,7 +13789,7 @@
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
@@ -14259,12 +13799,12 @@
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+          <t>SER_AU_ABLV_MONTHLY</t>
         </is>
       </c>
       <c r="AT70" t="n">
@@ -14272,47 +13812,47 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14344,12 +13884,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -14374,12 +13914,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -14388,50 +13928,33 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>SER_AU_ABLV_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ71" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr">
-        <is>
-          <t>SER_AU_ABLV_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -14441,12 +13964,12 @@
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -14461,12 +13984,12 @@
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
@@ -14498,17 +14021,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -14533,12 +14056,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -14547,160 +14070,68 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>SER_AU_ABLV_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>SER_AU_ABLV_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>Australian bat lyssavirus infection</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD72" t="inlineStr">
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE72" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG72" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>AU_NINDSS_current</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Australia NINDSS human Australian bat lyssavirus infection; explicitly distinct from rabies virus infection.</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN72" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP72" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr">
-        <is>
-          <t>SER_AU_ABLV_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
-      <c r="AV72" t="inlineStr">
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Australia NINDSS</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
@@ -14737,12 +14168,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -14767,12 +14198,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -14781,93 +14212,73 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>weekly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14894,17 +14305,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -14929,12 +14340,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -14943,168 +14354,73 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="P74" t="n">
-        <v>0</v>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>Lyssavirus infection (excluding rabies)</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD74" t="inlineStr">
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE74" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF74" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG74" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN74" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP74" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ74" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT74" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV74" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15136,12 +14452,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -15166,12 +14482,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -15180,93 +14496,73 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>weekly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15293,17 +14589,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -15328,12 +14624,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -15342,168 +14638,73 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>Lyssavirus infection (excluding rabies)</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD76" t="inlineStr">
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE76" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF76" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG76" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN76" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP76" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV76" t="inlineStr">
-        <is>
-          <t>jp_weekly</t>
-        </is>
-      </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15535,12 +14736,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -15565,12 +14766,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -15579,93 +14780,73 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>weekly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr">
-        <is>
-          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15692,217 +14873,5236 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>D214</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Lyssavirus infection excluding rabies</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
         <is>
           <t>非狂犬病狂犬病毒属感染</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection (excluding rabies)</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN80" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection (excluding rabies)</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN82" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection (excluding rabies)</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN84" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection (excluding rabies)</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SER_AU_ABLV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>SER_AU_ABLV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SER_AU_ABLV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>SER_AU_ABLV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Australian bat lyssavirus infection</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>AU_NINDSS_current</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Australia NINDSS human Australian bat lyssavirus infection; explicitly distinct from rabies virus infection.</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN88" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>SER_AU_ABLV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC88" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr"/>
+      <c r="AT89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr"/>
+      <c r="AT90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr"/>
+      <c r="AT91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr"/>
+      <c r="AT92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
+      <c r="AT93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
+      <c r="AT94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
+      <c r="AT96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection (excluding rabies)</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN98" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection (excluding rabies)</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN100" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" t="inlineStr">
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
         <is>
           <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V78" t="inlineStr">
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
         <is>
           <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="W78" t="inlineStr">
+      <c r="AT101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
         <is>
           <t>SRC_JP_NIID</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>Lyssavirus infection (excluding rabies)</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Y102" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
+      <c r="Z102" t="inlineStr">
         <is>
           <t>notification</t>
         </is>
       </c>
-      <c r="AA78" t="inlineStr">
+      <c r="AA102" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
+      <c r="AB102" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
+      <c r="AC102" t="inlineStr">
         <is>
           <t>country:JP:national</t>
         </is>
       </c>
-      <c r="AD78" t="inlineStr">
+      <c r="AD102" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE78" t="inlineStr">
+      <c r="AE102" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF78" t="inlineStr">
+      <c r="AF102" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="AG78" t="inlineStr">
+      <c r="AG102" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH78" t="inlineStr">
+      <c r="AH102" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI78" t="inlineStr">
+      <c r="AI102" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ78" t="inlineStr">
+      <c r="AJ102" t="inlineStr">
         <is>
           <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
-      <c r="AK78" t="inlineStr">
+      <c r="AK102" t="inlineStr">
         <is>
           <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
+      <c r="AM102" t="inlineStr">
         <is>
           <t>provisional; raw</t>
         </is>
       </c>
-      <c r="AN78" t="b">
+      <c r="AN102" t="b">
         <v>1</v>
       </c>
-      <c r="AO78" t="inlineStr">
+      <c r="AO102" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP78" t="inlineStr">
+      <c r="AP102" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ78" t="inlineStr">
+      <c r="AQ102" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS78" t="inlineStr">
+      <c r="AS102" t="inlineStr">
         <is>
           <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="AT78" t="n">
+      <c r="AT102" t="n">
         <v>1</v>
       </c>
-      <c r="AU78" t="inlineStr">
+      <c r="AU102" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV78" t="inlineStr">
+      <c r="AV102" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW78" t="inlineStr">
+      <c r="AW102" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
+      <c r="AX102" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY78" t="inlineStr">
+      <c r="AY102" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
+      <c r="AZ102" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA78" t="inlineStr">
+      <c r="BA102" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB78" t="inlineStr">
+      <c r="BB102" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC78" t="inlineStr">
+      <c r="BC102" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection (excluding rabies)</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Japan NIID human lyssavirus infection explicitly excluding rabies.</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN104" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>SER_JP_LYSSAVIRUS_EXCLUDING_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SER_AU_ABLV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>SER_AU_ABLV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>lyssavirus-infection-excluding-rabies</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D214</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Lyssavirus infection excluding rabies</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>非狂犬病狂犬病毒属感染</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SER_AU_ABLV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>SER_AU_ABLV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>Australian bat lyssavirus infection</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>AU_NINDSS_current</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Australia NINDSS human Australian bat lyssavirus infection; explicitly distinct from rabies virus infection.</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN106" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>SER_AU_ABLV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15939,7 +20139,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -16022,7 +20222,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -16032,7 +20232,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11">
@@ -16052,7 +20252,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
